--- a/data/TableS1_haypile_summary.xlsx
+++ b/data/TableS1_haypile_summary.xlsx
@@ -1,161 +1,168 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reiknistofnun-my.sharepoint.com/personal/isabel_lbhi_is/Documents/ISABEL/R/pika_invert_herbivory/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_5D73C1868BE7C5B83C2E1A9D1C5983179856AA07" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5ACA5854-08F4-41B7-8C34-DA23F57BC7B1}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Damage" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Damage" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
-  <si>
-    <t xml:space="preserve">species_group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dryas octopetala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polygonum bistorta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polygonum viviparum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salix reticulata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salix spp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vaccinium uliginosum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vaccinium vitis-idaea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cassiope tetragona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petasites frigidus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other forbs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graminoids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lichens and mosses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proportion damaged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total biomass (g)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="45">
+  <si>
+    <t>species_group</t>
+  </si>
+  <si>
+    <t>HP1</t>
+  </si>
+  <si>
+    <t>HP2</t>
+  </si>
+  <si>
+    <t>HP3</t>
+  </si>
+  <si>
+    <t>HP4</t>
+  </si>
+  <si>
+    <t>HP5</t>
+  </si>
+  <si>
+    <t>HP6</t>
+  </si>
+  <si>
+    <t>HP7</t>
+  </si>
+  <si>
+    <t>HP8</t>
+  </si>
+  <si>
+    <t>HP9</t>
+  </si>
+  <si>
+    <t>HP10</t>
+  </si>
+  <si>
+    <t>HP11</t>
+  </si>
+  <si>
+    <t>HP12</t>
+  </si>
+  <si>
+    <t>HP13</t>
+  </si>
+  <si>
+    <t>HP14</t>
+  </si>
+  <si>
+    <t>HP15</t>
+  </si>
+  <si>
+    <t>HP16</t>
+  </si>
+  <si>
+    <t>HP17</t>
+  </si>
+  <si>
+    <t>HP18</t>
+  </si>
+  <si>
+    <t>HP19</t>
+  </si>
+  <si>
+    <t>HP20</t>
+  </si>
+  <si>
+    <t>HP21</t>
+  </si>
+  <si>
+    <t>HP22</t>
+  </si>
+  <si>
+    <t>HP23</t>
+  </si>
+  <si>
+    <t>HP24</t>
+  </si>
+  <si>
+    <t>HP25</t>
+  </si>
+  <si>
+    <t>HP26</t>
+  </si>
+  <si>
+    <t>HP27</t>
+  </si>
+  <si>
+    <t>HP28</t>
+  </si>
+  <si>
+    <t>HP29</t>
+  </si>
+  <si>
+    <t>HP30</t>
+  </si>
+  <si>
+    <t>Dryas octopetala</t>
+  </si>
+  <si>
+    <t>Polygonum bistorta</t>
+  </si>
+  <si>
+    <t>Polygonum viviparum</t>
+  </si>
+  <si>
+    <t>Salix reticulata</t>
+  </si>
+  <si>
+    <t>Salix spp.</t>
+  </si>
+  <si>
+    <t>Vaccinium uliginosum</t>
+  </si>
+  <si>
+    <t>Vaccinium vitis-idaea</t>
+  </si>
+  <si>
+    <t>Cassiope tetragona</t>
+  </si>
+  <si>
+    <t>Petasites frigidus</t>
+  </si>
+  <si>
+    <t>Other forbs</t>
+  </si>
+  <si>
+    <t>Graminoids</t>
+  </si>
+  <si>
+    <t>Lichens and mosses</t>
+  </si>
+  <si>
+    <t>Proportion damaged</t>
+  </si>
+  <si>
+    <t>Total biomass (g)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -167,9 +174,9 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <b/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -202,13 +209,22 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -490,1546 +506,1450 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AE15"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="D2" s="2" t="n">
+      <c r="B2" s="1">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="D2" s="1">
         <v>0.12</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="F2" s="2" t="n">
+      <c r="E2" s="1">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="F2" s="1">
         <v>0.218</v>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>0.088</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0.282</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="J2" s="2" t="n">
+      <c r="G2" s="1">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="J2" s="1">
         <v>0.129</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>0.088</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="T2" s="2" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="U2" s="2" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="V2" s="2" t="n">
-        <v>0.358</v>
-      </c>
-      <c r="W2" s="2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="X2" s="2" t="n">
+      <c r="K2" s="1">
+        <v>0.42099999999999999</v>
+      </c>
+      <c r="L2" s="1">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M2" s="1">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="N2" s="1">
+        <v>6.2E-2</v>
+      </c>
+      <c r="O2" s="1">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2" s="1">
+        <v>2.3E-2</v>
+      </c>
+      <c r="T2" s="1">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="U2" s="1">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="V2" s="1">
+        <v>0.35799999999999998</v>
+      </c>
+      <c r="W2">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="X2" s="1">
         <v>0.219</v>
       </c>
-      <c r="Y2" s="2" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="Z2" s="2" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="AA2" s="2" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="AB2" s="2" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="AC2" s="2" t="n">
-        <v>0.202</v>
-      </c>
-      <c r="AD2" s="2" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="AE2" s="2" t="n">
-        <v>0.044</v>
+      <c r="Y2" s="1">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>32</v>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0.288</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="P3" s="2" t="n">
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1.2E-2</v>
+      </c>
+      <c r="I3">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="J3" s="1">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="K3" s="1">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="P3" s="1">
         <v>0.08</v>
       </c>
-      <c r="Q3" s="2" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
+      <c r="Q3" s="1">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3" s="1">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="T3">
+        <v>1E-3</v>
+      </c>
+      <c r="U3" s="1">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>0.009</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="F4" s="2" t="n">
+      <c r="B4" s="1">
+        <v>2E-3</v>
+      </c>
+      <c r="C4">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F4" s="1">
         <v>0.01</v>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="V4" s="2" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="W4" s="2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="2" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="AD4" s="2" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="AE4" s="2" t="n">
-        <v>0.004</v>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="I4" s="1">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J4" s="1">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="K4">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="L4">
+        <v>1E-3</v>
+      </c>
+      <c r="M4" s="1">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="N4" s="1">
+        <v>2E-3</v>
+      </c>
+      <c r="O4" s="1">
+        <v>2E-3</v>
+      </c>
+      <c r="P4" s="1">
+        <v>2E-3</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="T4" s="1">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="U4" s="1">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="V4" s="1">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="W4" s="1">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="X4">
+        <v>1E-3</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="1">
         <v>0.04</v>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G5" s="2" t="n">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1">
+        <v>6.2E-2</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G5" s="1">
         <v>0.214</v>
       </c>
-      <c r="H5" s="2" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="2" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="Y5" s="2" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="Z5" s="2" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="AA5" s="2" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="AB5" s="2" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="AC5" s="2" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="AD5" s="2" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="AE5" s="2" t="n">
-        <v>0.074</v>
+      <c r="H5" s="1">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="K5" s="1">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="L5" s="1">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>3.1E-2</v>
+      </c>
+      <c r="R5" s="1">
+        <v>2E-3</v>
+      </c>
+      <c r="S5" s="1">
+        <v>6.2E-2</v>
+      </c>
+      <c r="T5" s="1">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="U5" s="1">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="V5" s="1">
+        <v>1.4E-2</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5" s="1">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>2.4E-2</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>2.4E-2</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>0.673</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="G6" s="2" t="n">
+      <c r="B6" s="1">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2.4E-2</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="F6" s="1">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="G6" s="1">
         <v>0.215</v>
       </c>
-      <c r="H6" s="2" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="L6" s="2" t="n">
+      <c r="H6" s="1">
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.40699999999999997</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="L6" s="1">
         <v>0.436</v>
       </c>
-      <c r="M6" s="2" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="S6" s="2" t="n">
+      <c r="M6" s="1">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="N6" s="1">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="O6" s="1">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="R6" s="1">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="S6" s="1">
         <v>0.115</v>
       </c>
-      <c r="T6" s="2" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="U6" s="2" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="V6" s="2" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="W6" s="2" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="X6" s="2" t="n">
-        <v>0.358</v>
-      </c>
-      <c r="Y6" s="2" t="n">
-        <v>0.815</v>
-      </c>
-      <c r="Z6" s="2" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="AA6" s="2" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="AB6" s="2" t="n">
+      <c r="T6" s="1">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="U6" s="1">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="V6" s="1">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="W6" s="1">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0.35799999999999998</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="AB6" s="1">
         <v>0.191</v>
       </c>
-      <c r="AC6" s="2" t="n">
+      <c r="AC6" s="1">
         <v>0.246</v>
       </c>
-      <c r="AD6" s="2" t="n">
-        <v>0.448</v>
-      </c>
-      <c r="AE6" s="2" t="n">
+      <c r="AD6" s="1">
+        <v>0.44800000000000001</v>
+      </c>
+      <c r="AE6" s="1">
         <v>0.374</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>36</v>
       </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="2" t="n">
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1">
         <v>0.439</v>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="Q7" s="2" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="2" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
+      <c r="D7" s="1">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>1E-3</v>
+      </c>
+      <c r="P7" s="1">
+        <v>2.4E-2</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="V7">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="W7">
+        <v>1E-3</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>37</v>
       </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="U8" s="2" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="2" t="n">
-        <v>0.008</v>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="P8">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="T8">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="U8" s="1">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>38</v>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
         <v>0</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>39</v>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
         <v>0.183</v>
       </c>
-      <c r="O10" t="n">
-        <v>0.356</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="O10">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="P10">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="Q10">
         <v>0.03</v>
       </c>
-      <c r="R10" s="2" t="n">
-        <v>0.486</v>
-      </c>
-      <c r="S10" s="2" t="n">
+      <c r="R10" s="1">
+        <v>0.48599999999999999</v>
+      </c>
+      <c r="S10" s="1">
         <v>0.157</v>
       </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="AE10" t="n">
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="AA10">
+        <v>3.9E-2</v>
+      </c>
+      <c r="AB10">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="AC10">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="AD10">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AE10">
         <v>0.151</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>40</v>
       </c>
-      <c r="B11" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.287</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0.086</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="B11">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E11">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="F11">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="G11">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="H11">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="I11" s="1">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="J11">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="K11">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="L11">
         <v>0.12</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="O11">
+        <v>3.9E-2</v>
+      </c>
+      <c r="P11">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="Q11">
         <v>0.107</v>
       </c>
-      <c r="R11" t="n">
-        <v>0.071</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="R11">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="S11">
         <v>0.03</v>
       </c>
-      <c r="T11" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="U11" s="2" t="n">
-        <v>0.072</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.085</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="Y11" t="n">
+      <c r="T11">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="U11" s="1">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="V11">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="W11">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="X11">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="Y11">
         <v>0.06</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="Z11">
         <v>0.06</v>
       </c>
-      <c r="AA11" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.084</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.071</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.061</v>
+      <c r="AA11">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="AB11">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="AC11">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="AD11">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="AE11">
+        <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>41</v>
       </c>
-      <c r="B12" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.386</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.717</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.328</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="B12">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="C12">
+        <v>0.38600000000000001</v>
+      </c>
+      <c r="D12">
+        <v>0.71699999999999997</v>
+      </c>
+      <c r="E12">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="F12">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="G12">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="H12">
         <v>0.33</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.282</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="I12">
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="J12">
         <v>0.115</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>0.111</v>
       </c>
-      <c r="L12" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.881</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.428</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="L12">
+        <v>0.34699999999999998</v>
+      </c>
+      <c r="M12">
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="N12">
+        <v>0.42799999999999999</v>
+      </c>
+      <c r="O12">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="P12">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="Q12">
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="R12">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="S12">
         <v>0.34</v>
       </c>
-      <c r="T12" t="n">
-        <v>0.631</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="W12" t="n">
+      <c r="T12">
+        <v>0.63100000000000001</v>
+      </c>
+      <c r="U12">
+        <v>0.42299999999999999</v>
+      </c>
+      <c r="V12">
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="W12">
         <v>0.93</v>
       </c>
-      <c r="X12" t="n">
+      <c r="X12">
         <v>0.219</v>
       </c>
-      <c r="Y12" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.711</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="Y12">
+        <v>6.2E-2</v>
+      </c>
+      <c r="Z12">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="AA12">
+        <v>0.71099999999999997</v>
+      </c>
+      <c r="AB12">
         <v>0.19</v>
       </c>
-      <c r="AC12" t="n">
-        <v>0.261</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AC12">
+        <v>0.26100000000000001</v>
+      </c>
+      <c r="AD12">
         <v>0.31</v>
       </c>
-      <c r="AE12" t="n">
-        <v>0.239</v>
+      <c r="AE12">
+        <v>0.23899999999999999</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>42</v>
       </c>
-      <c r="B13" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="Z13" s="2" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.046</v>
+      <c r="B13">
+        <v>2.3E-2</v>
+      </c>
+      <c r="C13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="H13">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="I13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J13">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="K13">
+        <v>2.3E-2</v>
+      </c>
+      <c r="L13">
+        <v>1.6E-2</v>
+      </c>
+      <c r="M13">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="N13">
+        <v>1.6E-2</v>
+      </c>
+      <c r="O13">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="P13">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="Q13">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="R13">
+        <v>1E-3</v>
+      </c>
+      <c r="S13">
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="T13">
+        <v>1.6E-2</v>
+      </c>
+      <c r="U13">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="V13">
+        <v>2.4E-2</v>
+      </c>
+      <c r="W13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="X13">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="Y13">
+        <v>1.4E-2</v>
+      </c>
+      <c r="Z13">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="AA13">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="AB13">
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="AC13">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="AD13">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="AE13">
+        <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>43</v>
       </c>
-      <c r="B14" t="n">
-        <v>0.601</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="B14">
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="C14">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="D14">
         <v>0.107</v>
       </c>
-      <c r="E14" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="H14" t="n">
+      <c r="E14">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="F14">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="G14">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="H14">
         <v>0.222</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>0.186</v>
       </c>
-      <c r="J14" t="n">
-        <v>0.468</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.369</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="J14">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="K14">
+        <v>0.36899999999999999</v>
+      </c>
+      <c r="L14">
         <v>0.161</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>0.02</v>
       </c>
-      <c r="N14" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="R14" t="n">
+      <c r="N14">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="O14">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="P14">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="Q14">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="R14">
         <v>0.124</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S14">
         <v>0.16</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T14">
         <v>0.127</v>
       </c>
-      <c r="U14" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="V14" t="n">
+      <c r="U14">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="V14">
         <v>0.127</v>
       </c>
-      <c r="W14" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="X14" t="n">
+      <c r="W14">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="X14">
         <v>0.157</v>
       </c>
-      <c r="Y14" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="AC14" s="2" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.349</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0.176</v>
+      <c r="Y14">
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="Z14">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="AA14">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="AB14">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="AC14">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="AD14">
+        <v>0.34899999999999998</v>
+      </c>
+      <c r="AE14">
+        <v>0.17599999999999999</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>44</v>
       </c>
-      <c r="B15" t="n">
-        <v>21.876</v>
-      </c>
-      <c r="C15" t="n">
-        <v>10.001</v>
-      </c>
-      <c r="D15" t="n">
-        <v>18.129</v>
-      </c>
-      <c r="E15" t="n">
-        <v>12.329</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>19.547</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="B15">
+        <v>21.876000000000001</v>
+      </c>
+      <c r="C15">
+        <v>10.000999999999999</v>
+      </c>
+      <c r="D15">
+        <v>18.129000000000001</v>
+      </c>
+      <c r="E15">
+        <v>12.329000000000001</v>
+      </c>
+      <c r="F15">
+        <v>19.547000000000001</v>
+      </c>
+      <c r="G15">
         <v>12.516</v>
       </c>
-      <c r="H15" t="n">
-        <v>16.505</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="H15">
+        <v>16.504999999999999</v>
+      </c>
+      <c r="I15">
         <v>17.84</v>
       </c>
-      <c r="J15" s="2" t="n">
-        <v>18.356</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="J15">
+        <v>18.356000000000002</v>
+      </c>
+      <c r="K15">
         <v>19.009</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>12.878</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>7.58</v>
       </c>
-      <c r="N15" t="n">
-        <v>16.976</v>
-      </c>
-      <c r="O15" t="n">
-        <v>17.688</v>
-      </c>
-      <c r="P15" t="n">
-        <v>9.977</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="N15">
+        <v>16.975999999999999</v>
+      </c>
+      <c r="O15">
+        <v>17.687999999999999</v>
+      </c>
+      <c r="P15">
+        <v>9.9770000000000003</v>
+      </c>
+      <c r="Q15">
         <v>17.526</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R15">
         <v>12.028</v>
       </c>
-      <c r="S15" s="2" t="n">
-        <v>14.601</v>
-      </c>
-      <c r="T15" t="n">
+      <c r="S15">
+        <v>14.601000000000001</v>
+      </c>
+      <c r="T15">
         <v>13.38</v>
       </c>
-      <c r="U15" s="2" t="n">
-        <v>22.205</v>
-      </c>
-      <c r="V15" t="n">
+      <c r="U15">
+        <v>22.204999999999998</v>
+      </c>
+      <c r="V15">
         <v>15.36</v>
       </c>
-      <c r="W15" s="2" t="n">
+      <c r="W15">
         <v>15.215</v>
       </c>
-      <c r="X15" t="n">
-        <v>14.591</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>20.208</v>
-      </c>
-      <c r="Z15" t="n">
+      <c r="X15">
+        <v>14.590999999999999</v>
+      </c>
+      <c r="Y15">
+        <v>20.207999999999998</v>
+      </c>
+      <c r="Z15">
         <v>20.602</v>
       </c>
-      <c r="AA15" t="n">
-        <v>8.882</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>16.133</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>17.681</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>14.502</v>
-      </c>
-      <c r="AE15" t="n">
+      <c r="AA15">
+        <v>8.8819999999999997</v>
+      </c>
+      <c r="AB15">
+        <v>16.132999999999999</v>
+      </c>
+      <c r="AC15">
+        <v>17.681000000000001</v>
+      </c>
+      <c r="AD15">
+        <v>14.502000000000001</v>
+      </c>
+      <c r="AE15">
         <v>14.805</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="R16" s="2"/>
-      <c r="X16" s="2"/>
-      <c r="Y16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="X17" s="2"/>
-      <c r="Y17" s="2"/>
-      <c r="AC17" s="2"/>
-      <c r="AD17" s="2"/>
-    </row>
-    <row r="21">
-      <c r="AC21" s="2"/>
-    </row>
-    <row r="25">
-      <c r="P25" s="2"/>
-    </row>
-    <row r="26">
-      <c r="D26" s="2"/>
-      <c r="K26" s="2"/>
-    </row>
-    <row r="28">
-      <c r="E28" s="2"/>
-    </row>
-    <row r="30">
-      <c r="V30" s="2"/>
-      <c r="Z30" s="2"/>
-      <c r="AC30" s="2"/>
-    </row>
-    <row r="32">
-      <c r="S32" s="2"/>
-      <c r="T32" s="2"/>
-      <c r="Y32" s="2"/>
-      <c r="Z32" s="2"/>
-    </row>
-    <row r="34">
-      <c r="B34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="W34" s="2"/>
-    </row>
-    <row r="36">
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-    </row>
-    <row r="38">
-      <c r="U38" s="2"/>
-    </row>
-    <row r="39">
-      <c r="D39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="O39" s="2"/>
-      <c r="P39" s="2"/>
-      <c r="Q39" s="2"/>
-      <c r="R39" s="2"/>
-      <c r="S39" s="2"/>
-      <c r="T39" s="2"/>
-      <c r="AA39" s="2"/>
-      <c r="AB39" s="2"/>
-      <c r="AC39" s="2"/>
-      <c r="AD39" s="2"/>
-    </row>
-    <row r="41">
-      <c r="H41" s="2"/>
-    </row>
-    <row r="43">
-      <c r="H43" s="2"/>
-    </row>
-    <row r="44">
-      <c r="P44" s="2"/>
-      <c r="T44" s="2"/>
-      <c r="Y44" s="2"/>
-    </row>
-    <row r="47">
-      <c r="E47" s="2"/>
-    </row>
-    <row r="48">
-      <c r="C48" s="2"/>
-      <c r="Q48" s="2"/>
-      <c r="R48" s="2"/>
-      <c r="S48" s="2"/>
-    </row>
-    <row r="49">
-      <c r="E49" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:AE13"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2124,7 +2044,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -2219,7 +2139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -2314,7 +2234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -2409,7 +2329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -2504,7 +2424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -2599,7 +2519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -2694,7 +2614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -2789,7 +2709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -2884,7 +2804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -2979,7 +2899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -3074,7 +2994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -3169,7 +3089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -3266,6 +3186,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>